--- a/output/pdf_financials_xlsx/TLG.xlsx
+++ b/output/pdf_financials_xlsx/TLG.xlsx
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.680594</v>
+        <v>-0.680594</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.601294</v>
+        <v>-0.601294</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.630696</v>
+        <v>-0.630696</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>30.43107</v>
+        <v>-30.43107</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>19.648738</v>
+        <v>-19.648738</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.413379</v>
+        <v>-18.413379</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>74.955164</v>
+        <v>-74.955164</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.242416</v>
+        <v>-36.242416</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-5.575399</v>
@@ -1271,31 +1271,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.680594</v>
+        <v>-0.680594</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.601294</v>
+        <v>-0.601294</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.630696</v>
+        <v>-0.630696</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>30.43107</v>
+        <v>-30.43107</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.648738</v>
+        <v>-19.648738</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.413379</v>
+        <v>-18.413379</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>74.955164</v>
+        <v>-74.955164</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>36.242416</v>
+        <v>-36.242416</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-5.575399</v>
@@ -1400,31 +1400,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.680594</v>
+        <v>-0.680594</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.601294</v>
+        <v>-0.601294</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.630696</v>
+        <v>-0.630696</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>30.43107</v>
+        <v>-30.43107</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>19.648738</v>
+        <v>-19.648738</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>18.413379</v>
+        <v>-18.413379</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>74.955164</v>
+        <v>-74.955164</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>36.242416</v>
+        <v>-36.242416</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-5.575399</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>3.240924</v>
+        <v>-3.240924</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1546,22 +1546,22 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.7674</v>
+        <v>-15.7674</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>33.440736</v>
+        <v>-33.440736</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>53.104697</v>
+        <v>-53.104697</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>80.05817</v>
+        <v>-80.05817</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>133.848507</v>
+        <v>-133.848507</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>201.346756</v>
+        <v>-201.346756</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>185.846633</v>
@@ -1580,31 +1580,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.680594</v>
+        <v>-0.680594</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.601294</v>
+        <v>-0.601294</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.630696</v>
+        <v>-0.630696</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>30.43107</v>
+        <v>-30.43107</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19.648738</v>
+        <v>-19.648738</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18.413379</v>
+        <v>-18.413379</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>74.955164</v>
+        <v>-74.955164</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>36.242416</v>
+        <v>-36.242416</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-5.575399</v>
@@ -1666,31 +1666,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.680594</v>
+        <v>-0.680594</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.601294</v>
+        <v>-0.601294</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.630696</v>
+        <v>-0.630696</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.46476</v>
+        <v>-30.39738</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.867809</v>
+        <v>-19.429667</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19.288298</v>
+        <v>-17.53846</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>76.070835</v>
+        <v>-73.839493</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>37.668353</v>
+        <v>-34.816479</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-4.046956</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -4445,40 +4445,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.7866</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1755</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.050305</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.331632</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.195576</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.047793</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.834969</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.988801</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>12.049119</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.655116</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.513038</v>
       </c>
     </row>
     <row r="93">
@@ -8078,7 +8078,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -9334,7 +9338,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -10208,7 +10216,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -11332,7 +11344,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -12384,7 +12400,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.7866</v>
       </c>
@@ -27608,22 +27628,22 @@
         </is>
       </c>
       <c r="I286" s="5" t="n">
-        <v>30.43107</v>
+        <v>-30.43107</v>
       </c>
       <c r="J286" s="5" t="n">
-        <v>19.648738</v>
+        <v>-19.648738</v>
       </c>
       <c r="K286" s="5" t="n">
-        <v>18.413379</v>
+        <v>-18.413379</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>74.955164</v>
+        <v>-74.955164</v>
       </c>
       <c r="M286" s="5" t="n">
-        <v>36.242416</v>
+        <v>-36.242416</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>5.575399</v>
+        <v>-5.575399</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -30511,10 +30531,10 @@
         </is>
       </c>
       <c r="H325" s="5" t="n">
-        <v>0.630696</v>
+        <v>-0.630696</v>
       </c>
       <c r="I325" s="5" t="n">
-        <v>30.43107</v>
+        <v>-30.43107</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -31255,10 +31275,10 @@
         </is>
       </c>
       <c r="F335" s="5" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>0.601294</v>
+        <v>-0.601294</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
@@ -32000,10 +32020,10 @@
         </is>
       </c>
       <c r="E345" s="5" t="n">
-        <v>0.680594</v>
+        <v>-0.680594</v>
       </c>
       <c r="F345" s="5" t="n">
-        <v>0.000234</v>
+        <v>-0.000234</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TLG.xlsx
+++ b/output/pdf_financials_xlsx/TLG.xlsx
@@ -891,28 +891,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.145647</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.230918</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.124568</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.031678</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.20305</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.247815</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.411848</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.694188</v>
       </c>
     </row>
     <row r="13">
@@ -1592,28 +1592,28 @@
         <v>-0.630696</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-30.43107</v>
+        <v>-30.285423</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-19.648738</v>
+        <v>-19.41782</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-18.413379</v>
+        <v>-18.288811</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-74.955164</v>
+        <v>-74.923486</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-36.242416</v>
+        <v>-36.039366</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.575399</v>
+        <v>-5.823214</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-34.268174</v>
+        <v>-34.680022</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-39.360546</v>
+        <v>-40.054734</v>
       </c>
     </row>
     <row r="28">
@@ -1678,28 +1678,28 @@
         <v>-0.630696</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-30.39738</v>
+        <v>-30.251733</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-19.429667</v>
+        <v>-19.198749</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-17.53846</v>
+        <v>-17.413892</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-73.839493</v>
+        <v>-73.80781500000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-34.816479</v>
+        <v>-34.613429</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.046956</v>
+        <v>-4.294771</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-32.843871</v>
+        <v>-33.255719</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-39.360546</v>
+        <v>-40.054734</v>
       </c>
     </row>
     <row r="30">
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.215048</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010553</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.046595</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.215048</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010553</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.046595</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -5899,25 +5899,25 @@
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08502999999999999</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.50911</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-1.198549</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.678101</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.6085199999999999</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.646088</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.93572</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -5946,25 +5946,25 @@
         </is>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08502999999999999</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.50911</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-1.198549</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.678101</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.6085199999999999</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.646088</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.93572</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -7150,7 +7150,11 @@
           <t>Reclamation deposits 10</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8716,7 +8720,11 @@
           <t>Reclamation deposits 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -9626,7 +9634,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -10594,7 +10606,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11722,7 +11738,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -12174,7 +12194,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -14330,7 +14350,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -16222,7 +16246,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -17420,7 +17448,11 @@
           <t>Refund of reclamation deposit 8</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -18624,7 +18656,11 @@
           <t>Lease payments 3,9</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -18924,7 +18960,11 @@
           <t>Refund of reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -20524,7 +20564,11 @@
           <t>Equipment lease payments</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -20752,7 +20796,11 @@
           <t>Payment of reclamation deposit</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -24634,7 +24682,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -27010,7 +27058,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">

--- a/output/pdf_financials_xlsx/TLG.xlsx
+++ b/output/pdf_financials_xlsx/TLG.xlsx
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.637015</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
@@ -14568,7 +14568,11 @@
           <t>Acquisition of investment</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21414,7 +21418,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
